--- a/Templates/Template_CKGBalita.xlsx
+++ b/Templates/Template_CKGBalita.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\AutoCKG\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4B75E9-C952-477E-8F98-08FC53D867E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A775A30A-2F61-4A32-9768-99B11E2FA3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,164 +362,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
-  <si>
-    <t>NIK</t>
-  </si>
-  <si>
-    <t>Nama Lengkap</t>
-  </si>
-  <si>
-    <t>Tanggal lahir</t>
-  </si>
-  <si>
-    <t>Jenis Kelamin</t>
-  </si>
-  <si>
-    <t>No Whatsapp</t>
-  </si>
-  <si>
-    <t>Detail Domisili</t>
-  </si>
-  <si>
-    <t>Berat Badan</t>
-  </si>
-  <si>
-    <t>Tinggi Badan</t>
-  </si>
-  <si>
-    <t>Sistol</t>
-  </si>
-  <si>
-    <t>Diastol</t>
-  </si>
-  <si>
-    <t>Gula Darah</t>
-  </si>
-  <si>
-    <t>Keterangan</t>
-  </si>
-  <si>
-    <t>Tidak memiliki disabilitas</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>normal</t>
-  </si>
-  <si>
-    <t>jumlahCoba</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>notif</t>
-  </si>
-  <si>
-    <t>Provinsi</t>
-  </si>
-  <si>
-    <t>Kota</t>
-  </si>
-  <si>
-    <t>Kecamatan</t>
-  </si>
-  <si>
-    <t>Kelurahan</t>
-  </si>
-  <si>
-    <t>Lainnya</t>
-  </si>
-  <si>
-    <t>Hamil</t>
-  </si>
-  <si>
-    <t>Status Pernikahan</t>
-  </si>
-  <si>
-    <t>Penyandang Disabilitas</t>
-  </si>
-  <si>
-    <t>Pekerjaan</t>
-  </si>
-  <si>
-    <t>Lingkar Perut</t>
-  </si>
-  <si>
-    <t>Faktor Risiko Kanker Usus</t>
-  </si>
-  <si>
-    <t>TIDAK</t>
-  </si>
-  <si>
-    <t>Faktor Risiko TB - Dewasa &amp; Lansia</t>
-  </si>
-  <si>
-    <t>Hati</t>
-  </si>
-  <si>
-    <t>Kanker Leher Rahim</t>
-  </si>
-  <si>
-    <t>Kesehatan Jiwa</t>
-  </si>
-  <si>
-    <t>BAIK</t>
-  </si>
-  <si>
-    <t>Penapisan Risiko Kanker Paru</t>
-  </si>
-  <si>
-    <t>NORMAL</t>
-  </si>
-  <si>
-    <t>Perilaku Merokok</t>
-  </si>
-  <si>
-    <t>Tingkat Aktivitas Fisik (sedang dan berat)</t>
-  </si>
-  <si>
-    <t>Disabilitas</t>
-  </si>
-  <si>
-    <t>Non disabilitas</t>
-  </si>
-  <si>
-    <t>tidak</t>
-  </si>
-  <si>
-    <t>Jawa Timur</t>
-  </si>
-  <si>
-    <t>Kota Malang</t>
-  </si>
-  <si>
-    <t>Kedungkandang</t>
-  </si>
-  <si>
-    <t>Buring</t>
-  </si>
-  <si>
-    <t>3573031702000003</t>
-  </si>
-  <si>
-    <t>AHMAD DWI CANDRA GUNAWAN</t>
-  </si>
-  <si>
-    <t>KH MALIK DALAM 1 RT 1 RW 3 BURING</t>
-  </si>
-  <si>
-    <t>60 kg</t>
-  </si>
-  <si>
-    <t>165 cm</t>
-  </si>
-  <si>
-    <t>80 cm</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="B1:AD2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.125" style="1" bestFit="1" customWidth="1"/>
@@ -976,194 +819,17 @@
     <col min="31" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="1" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2" ca="1" si="0">TEXT(DATE(IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))), VALUE(MID(A2,9,2)), IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "dd-mm-yyyy")</f>
-        <v>17-02-2000</v>
-      </c>
-      <c r="D2" s="2" t="str">
-        <f t="shared" ref="D2" si="1">IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
-        <v>Laki-laki</v>
-      </c>
-      <c r="E2" s="1">
-        <v>85230186668</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>34</v>
-      </c>
+    <row r="2" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="D2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Templates/Template_CKGBalita.xlsx
+++ b/Templates/Template_CKGBalita.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\AutoCKG\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A775A30A-2F61-4A32-9768-99B11E2FA3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70783E14-D3F2-4293-9858-3D3077B50BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,7 +362,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>ssssss</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -784,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AD2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.125" style="1" bestFit="1" customWidth="1"/>
@@ -819,7 +823,7 @@
     <col min="31" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
       <c r="Y1" s="3"/>
@@ -828,7 +832,10 @@
       <c r="AB1" s="3"/>
       <c r="AC1" s="3"/>
     </row>
-    <row r="2" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="D2" s="2"/>
     </row>
   </sheetData>
